--- a/cucumber-for-appian/src/test/resources/testdata/Regression/03_SMB_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/Regression/03_SMB_Regression.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="220">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -398,7 +398,7 @@
     <t>YES</t>
   </si>
   <si>
-    <t>No, it is for a used asset</t>
+    <t>Used</t>
   </si>
   <si>
     <t>Dealer</t>
@@ -425,6 +425,9 @@
     <t>$1,500</t>
   </si>
   <si>
+    <t>$0.00</t>
+  </si>
+  <si>
     <t>monthly in advance</t>
   </si>
   <si>
@@ -443,92 +446,95 @@
     <t>71kWh AWD</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>AUDIA1VIN12345678</t>
+  </si>
+  <si>
+    <t>AUDIA1REG123456</t>
+  </si>
+  <si>
+    <t>New Application[2]</t>
+  </si>
+  <si>
+    <t>WD HOMES SERVICES</t>
+  </si>
+  <si>
+    <t>56 Kimbler Rd, Roma QLD 4455</t>
+  </si>
+  <si>
+    <t>C MANUFACTURING</t>
+  </si>
+  <si>
+    <t>113 Dairy Product Manufacturing</t>
+  </si>
+  <si>
+    <t>DAIRY PRODUCTS</t>
+  </si>
+  <si>
+    <t>DAIRY PRODUCT ADVERTISEMENT</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>Jensen</t>
+  </si>
+  <si>
+    <t>Winchester</t>
+  </si>
+  <si>
+    <t>NZ Citizen</t>
+  </si>
+  <si>
+    <t>27/05/1981</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Renting</t>
+  </si>
+  <si>
+    <t>chandu.nagu+60@gmail.com</t>
+  </si>
+  <si>
+    <t>Learners Permit</t>
+  </si>
+  <si>
+    <t>Car Licence (C)</t>
+  </si>
+  <si>
+    <t>QLD</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>YES, I DO HAVE SUFFICIENT ONGOING MONTHLY CASHFLOW TO MEET MY REPAYMENTS UNDER THIS FACILITY.</t>
+  </si>
+  <si>
+    <t>Select All Privacy Consent check boxes</t>
+  </si>
+  <si>
+    <t>C:\Users\HP\Downloads\Rental_Agreement_Document.pdf</t>
+  </si>
+  <si>
     <t>C:\Users\HP\Downloads\DealerQuote.pdf</t>
   </si>
   <si>
-    <t>AUDIA1VIN12345678</t>
-  </si>
-  <si>
-    <t>AUDIA1REG123456</t>
-  </si>
-  <si>
-    <t>New Application[2]</t>
-  </si>
-  <si>
-    <t>WD HOMES SERVICES</t>
-  </si>
-  <si>
-    <t>56 Kimbler Rd, Roma QLD 4455</t>
-  </si>
-  <si>
-    <t>C MANUFACTURING</t>
-  </si>
-  <si>
-    <t>113 Dairy Product Manufacturing</t>
-  </si>
-  <si>
-    <t>DAIRY PRODUCTS</t>
-  </si>
-  <si>
-    <t>DAIRY PRODUCT ADVERTISEMENT</t>
-  </si>
-  <si>
-    <t>Dean</t>
-  </si>
-  <si>
-    <t>Jensen</t>
-  </si>
-  <si>
-    <t>Winchester</t>
-  </si>
-  <si>
-    <t>NZ Citizen</t>
-  </si>
-  <si>
-    <t>27/05/1981</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Renting</t>
-  </si>
-  <si>
-    <t>chandu.nagu+60@gmail.com</t>
-  </si>
-  <si>
-    <t>Learners Permit</t>
-  </si>
-  <si>
-    <t>Car Licence (C)</t>
-  </si>
-  <si>
-    <t>QLD</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>YES, I DO HAVE SUFFICIENT ONGOING MONTHLY CASHFLOW TO MEET MY REPAYMENTS UNDER THIS FACILITY.</t>
-  </si>
-  <si>
-    <t>Select All Privacy Consent check boxes</t>
-  </si>
-  <si>
-    <t>C:\Users\HP\Downloads\Rental_Agreement_Document.pdf</t>
-  </si>
-  <si>
-    <t>APP-724</t>
-  </si>
-  <si>
-    <t>SMB-00001054
-SMB-00001054</t>
+    <t>APP-726</t>
+  </si>
+  <si>
+    <t>SMB-00001059
+SMB-00001059</t>
   </si>
   <si>
     <t>Processing</t>
   </si>
   <si>
-    <t>19 Mar 2026 07:12 AM</t>
+    <t>25 Mar 2026 05:06 AM</t>
   </si>
   <si>
     <t>Automation Introducer</t>
@@ -537,25 +543,10 @@
     <t>TC002</t>
   </si>
   <si>
-    <t>Yes, it is for a new asset</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>$0.00</t>
-  </si>
-  <si>
     <t>Monthly in Advance</t>
   </si>
   <si>
-    <t>36 Months</t>
-  </si>
-  <si>
-    <t>TOYOTAVIN12345678</t>
-  </si>
-  <si>
-    <t>TOYOTAREG123456</t>
+    <t>71KWH AWD</t>
   </si>
   <si>
     <t>TOYOTAENG123456</t>
@@ -629,6 +620,75 @@
   </si>
   <si>
     <t>others</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>Yes, it is for a new asset</t>
+  </si>
+  <si>
+    <t>Finance Lease with Services</t>
+  </si>
+  <si>
+    <t>Saturn Blue metallic</t>
+  </si>
+  <si>
+    <t>Grey Synthetic leather</t>
+  </si>
+  <si>
+    <t>$156,000</t>
+  </si>
+  <si>
+    <t>Roadside Assistance</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>$5,000.00</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>${TC003.Application Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Quote Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Client or Applicant}</t>
+  </si>
+  <si>
+    <t>${TC003.Last Updated User}</t>
+  </si>
+  <si>
+    <t>$72,053.37</t>
+  </si>
+  <si>
+    <t>$671,875.80</t>
+  </si>
+  <si>
+    <t>$1,145.61</t>
+  </si>
+  <si>
+    <t>$15,524.74</t>
+  </si>
+  <si>
+    <t>Dealer Pricing</t>
+  </si>
+  <si>
+    <t>54.32%</t>
+  </si>
+  <si>
+    <t>Conditional Approval</t>
+  </si>
+  <si>
+    <t>Copy of current council rates notice to be provided to confirm property ownership.</t>
   </si>
   <si>
     <r>
@@ -659,75 +719,6 @@
       </rPr>
       <t>' document.</t>
     </r>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>Operating Lease</t>
-  </si>
-  <si>
-    <t>Eclipse Black</t>
-  </si>
-  <si>
-    <t>Grey Synthetic leather</t>
-  </si>
-  <si>
-    <t>Roadside Assistance</t>
-  </si>
-  <si>
-    <t>NSW</t>
-  </si>
-  <si>
-    <t>$5,000.00</t>
-  </si>
-  <si>
-    <t>TC004</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>48 months</t>
-  </si>
-  <si>
-    <t>71KWH AWD</t>
-  </si>
-  <si>
-    <t>${TC003.Application Number}</t>
-  </si>
-  <si>
-    <t>${TC003.Quote Number}</t>
-  </si>
-  <si>
-    <t>${TC003.Client or Applicant}</t>
-  </si>
-  <si>
-    <t>${TC003.Last Updated User}</t>
-  </si>
-  <si>
-    <t>$72,053.37</t>
-  </si>
-  <si>
-    <t>$671,875.80</t>
-  </si>
-  <si>
-    <t>$1,145.61</t>
-  </si>
-  <si>
-    <t>$15,524.74</t>
-  </si>
-  <si>
-    <t>Dealer Pricing</t>
-  </si>
-  <si>
-    <t>54.32%</t>
-  </si>
-  <si>
-    <t>Conditional Approval</t>
-  </si>
-  <si>
-    <t>Copy of current council rates notice to be provided to confirm property ownership.</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1410,7 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1433,8 +1424,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1808,101 +1799,128 @@
   <dimension ref="A1:DO25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.11111111111111" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="8.11111111111111" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="16.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="12.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="16.3333333333333" customWidth="1"/>
-    <col min="9" max="9" width="9.77777777777778" customWidth="1"/>
-    <col min="10" max="10" width="19.3333333333333" customWidth="1"/>
-    <col min="11" max="12" width="8.44444444444444" customWidth="1"/>
-    <col min="13" max="13" width="9.55555555555556" customWidth="1"/>
-    <col min="14" max="14" width="17.5555555555556" customWidth="1"/>
-    <col min="15" max="15" width="10.7777777777778" customWidth="1"/>
-    <col min="16" max="16" width="10.8888888888889" customWidth="1"/>
-    <col min="17" max="17" width="14.5555555555556" customWidth="1"/>
-    <col min="18" max="18" width="6.88888888888889" customWidth="1"/>
-    <col min="19" max="19" width="5.77777777777778" customWidth="1"/>
-    <col min="20" max="20" width="6.77777777777778" customWidth="1"/>
-    <col min="21" max="21" width="12.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="8.33333333333333" customWidth="1"/>
-    <col min="23" max="23" width="11.6666666666667" customWidth="1"/>
-    <col min="24" max="24" width="9.11111111111111" customWidth="1"/>
-    <col min="25" max="25" width="19.6666666666667" customWidth="1"/>
-    <col min="26" max="26" width="10.5555555555556" customWidth="1"/>
-    <col min="27" max="27" width="6.55555555555556" hidden="1" customWidth="1"/>
-    <col min="28" max="35" width="11.5555555555556" customWidth="1"/>
-    <col min="37" max="37" width="8.55555555555556" customWidth="1"/>
-    <col min="38" max="39" width="8.44444444444444" customWidth="1"/>
-    <col min="40" max="40" width="10.5555555555556" customWidth="1"/>
-    <col min="41" max="41" width="10" customWidth="1"/>
-    <col min="43" max="43" width="6.33333333333333" customWidth="1"/>
-    <col min="44" max="44" width="14.5555555555556" customWidth="1"/>
-    <col min="45" max="45" width="6.88888888888889" customWidth="1"/>
-    <col min="46" max="46" width="5.77777777777778" customWidth="1"/>
-    <col min="47" max="47" width="7.88888888888889" customWidth="1"/>
-    <col min="48" max="48" width="32.3333333333333" customWidth="1"/>
-    <col min="49" max="49" width="8.44444444444444" customWidth="1"/>
-    <col min="50" max="52" width="12.1111111111111" customWidth="1"/>
-    <col min="53" max="53" width="13.6666666666667" customWidth="1"/>
-    <col min="54" max="54" width="15.3333333333333" customWidth="1"/>
-    <col min="55" max="55" width="21.3333333333333" customWidth="1"/>
-    <col min="56" max="56" width="12.4444444444444" customWidth="1"/>
-    <col min="57" max="57" width="15.8888888888889" customWidth="1"/>
-    <col min="58" max="58" width="21.4444444444444" customWidth="1"/>
-    <col min="59" max="59" width="18.6666666666667" customWidth="1"/>
-    <col min="60" max="60" width="18.3333333333333" customWidth="1"/>
-    <col min="61" max="61" width="19.1111111111111" customWidth="1"/>
-    <col min="62" max="62" width="7.22222222222222" customWidth="1"/>
-    <col min="63" max="63" width="7.77777777777778" customWidth="1"/>
-    <col min="64" max="64" width="12.6666666666667" customWidth="1"/>
-    <col min="65" max="65" width="10.1111111111111" customWidth="1"/>
-    <col min="66" max="66" width="11.8888888888889" customWidth="1"/>
-    <col min="67" max="67" width="7.66666666666667" customWidth="1"/>
-    <col min="68" max="68" width="10.3333333333333" customWidth="1"/>
-    <col min="69" max="69" width="10.1111111111111" customWidth="1"/>
-    <col min="70" max="70" width="12" customWidth="1"/>
-    <col min="71" max="71" width="12.1111111111111" customWidth="1"/>
-    <col min="72" max="72" width="8.66666666666667" customWidth="1"/>
-    <col min="73" max="73" width="10.1111111111111" customWidth="1"/>
-    <col min="74" max="74" width="9.22222222222222" customWidth="1"/>
-    <col min="75" max="75" width="12.1111111111111" customWidth="1"/>
-    <col min="76" max="76" width="13.5555555555556" customWidth="1"/>
-    <col min="77" max="77" width="10.1111111111111" customWidth="1"/>
-    <col min="78" max="79" width="23.1111111111111" customWidth="1"/>
-    <col min="80" max="80" width="7.44444444444444" customWidth="1"/>
-    <col min="81" max="81" width="10.3333333333333" customWidth="1"/>
-    <col min="82" max="82" width="8.55555555555556" customWidth="1"/>
-    <col min="83" max="83" width="9.66666666666667" customWidth="1"/>
-    <col min="84" max="84" width="13.6666666666667" customWidth="1"/>
-    <col min="85" max="85" width="11.1111111111111" customWidth="1"/>
-    <col min="86" max="86" width="14.6666666666667" customWidth="1"/>
-    <col min="87" max="87" width="28.4444444444444" customWidth="1"/>
-    <col min="88" max="88" width="25.6666666666667" customWidth="1"/>
-    <col min="89" max="89" width="14.6666666666667" customWidth="1"/>
-    <col min="90" max="90" width="32.1111111111111" customWidth="1"/>
-    <col min="91" max="91" width="35.3333333333333" customWidth="1"/>
-    <col min="92" max="103" width="14.6666666666667" customWidth="1"/>
-    <col min="104" max="104" width="9.22222222222222" customWidth="1"/>
-    <col min="105" max="105" width="6.22222222222222" customWidth="1"/>
-    <col min="106" max="118" width="14.6666666666667" customWidth="1"/>
-    <col min="119" max="119" width="27" customWidth="1"/>
+    <col min="1" max="1" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="2" max="2" width="8.77777777777778" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.8888888888889" style="6" customWidth="1"/>
+    <col min="4" max="5" width="6.77777777777778" style="6" customWidth="1"/>
+    <col min="6" max="6" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.7777777777778" style="6" customWidth="1"/>
+    <col min="8" max="8" width="18.5555555555556" style="6" customWidth="1"/>
+    <col min="9" max="9" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="10" max="10" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="11" max="12" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="13" max="13" width="8.77777777777778" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16.3333333333333" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="16" max="16" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="17" max="17" width="13" style="6" customWidth="1"/>
+    <col min="18" max="18" width="6.77777777777778" style="6" customWidth="1"/>
+    <col min="19" max="20" width="6.66666666666667" style="6" customWidth="1"/>
+    <col min="21" max="21" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="22" max="22" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="23" max="24" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="25" max="25" width="13" style="6" customWidth="1"/>
+    <col min="26" max="26" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="27" max="27" width="6.66666666666667" style="6" customWidth="1"/>
+    <col min="28" max="28" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="29" max="29" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="30" max="30" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="31" max="31" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="32" max="32" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="33" max="33" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="34" max="34" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="35" max="35" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="36" max="36" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="37" max="37" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="38" max="39" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="40" max="41" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="42" max="42" width="6.77777777777778" style="6" customWidth="1"/>
+    <col min="43" max="43" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="44" max="44" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="45" max="45" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="46" max="46" width="5.66666666666667" style="6" customWidth="1"/>
+    <col min="47" max="47" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="48" max="48" width="25.2222222222222" style="6" customWidth="1"/>
+    <col min="49" max="49" width="7.77777777777778" style="6" customWidth="1"/>
+    <col min="50" max="50" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="51" max="51" width="11.7777777777778" style="6" customWidth="1"/>
+    <col min="52" max="52" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="53" max="53" width="13" style="6" customWidth="1"/>
+    <col min="54" max="54" width="12.8888888888889" style="6" customWidth="1"/>
+    <col min="55" max="55" width="17.7777777777778" style="6" customWidth="1"/>
+    <col min="56" max="56" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="57" max="57" width="14.7777777777778" style="6" customWidth="1"/>
+    <col min="58" max="58" width="17.4444444444444" style="6" customWidth="1"/>
+    <col min="59" max="59" width="17.7777777777778" style="6" customWidth="1"/>
+    <col min="60" max="60" width="14.7777777777778" style="6" customWidth="1"/>
+    <col min="61" max="61" width="15.2222222222222" style="6" customWidth="1"/>
+    <col min="62" max="62" width="6.33333333333333" style="6" customWidth="1"/>
+    <col min="63" max="63" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="64" max="64" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="65" max="65" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="66" max="66" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="67" max="67" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="68" max="69" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="70" max="70" width="10.6666666666667" style="6" customWidth="1"/>
+    <col min="71" max="71" width="11.7777777777778" style="6" customWidth="1"/>
+    <col min="72" max="72" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="73" max="73" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="74" max="74" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="75" max="75" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="76" max="76" width="25.2222222222222" style="6" customWidth="1"/>
+    <col min="77" max="77" width="13" style="6" customWidth="1"/>
+    <col min="78" max="78" width="43" style="6" customWidth="1"/>
+    <col min="79" max="79" width="20.7777777777778" style="6" customWidth="1"/>
+    <col min="80" max="80" width="7.44444444444444" style="6" customWidth="1"/>
+    <col min="81" max="81" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="82" max="82" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="83" max="83" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="84" max="84" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="85" max="85" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="86" max="86" width="13.7777777777778" style="6" customWidth="1"/>
+    <col min="87" max="87" width="27.7777777777778" style="6" customWidth="1"/>
+    <col min="88" max="88" width="23" style="6" customWidth="1"/>
+    <col min="89" max="89" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="90" max="90" width="27.7777777777778" style="6" customWidth="1"/>
+    <col min="91" max="91" width="21.7777777777778" style="6" customWidth="1"/>
+    <col min="92" max="92" width="13.7777777777778" style="6" customWidth="1"/>
+    <col min="93" max="93" width="13" style="6" customWidth="1"/>
+    <col min="94" max="95" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="96" max="96" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="97" max="97" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="98" max="98" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="99" max="99" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="100" max="101" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="102" max="102" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="103" max="103" width="10.7777777777778" style="6" customWidth="1"/>
+    <col min="104" max="104" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="105" max="105" width="6.66666666666667" style="6" customWidth="1"/>
+    <col min="106" max="106" width="8.55555555555556" style="6" customWidth="1"/>
+    <col min="107" max="107" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="108" max="108" width="12.7777777777778" style="6" customWidth="1"/>
+    <col min="109" max="109" width="13" style="6" customWidth="1"/>
+    <col min="110" max="112" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="113" max="113" width="9.77777777777778" style="6" customWidth="1"/>
+    <col min="114" max="114" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="115" max="115" width="14.1111111111111" style="6" customWidth="1"/>
+    <col min="116" max="116" width="11.7777777777778" style="6" customWidth="1"/>
+    <col min="117" max="117" width="13.7777777777778" style="6" customWidth="1"/>
+    <col min="118" max="118" width="11.8888888888889" style="6" customWidth="1"/>
+    <col min="119" max="119" width="24.7777777777778" style="6" customWidth="1"/>
+    <col min="120" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="70" customHeight="1" spans="1:119">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
@@ -2294,7 +2312,9 @@
       <c r="P2" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="Q2" s="9"/>
+      <c r="Q2" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="R2" s="9" t="s">
         <v>128</v>
       </c>
@@ -2310,11 +2330,11 @@
       <c r="V2" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="W2" s="9" t="s">
-        <v>128</v>
+      <c r="W2" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="X2" s="9">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="Y2" s="8">
         <v>5</v>
@@ -2322,9 +2342,7 @@
       <c r="Z2" s="8">
         <v>30</v>
       </c>
-      <c r="AA2" s="9" t="s">
-        <v>128</v>
-      </c>
+      <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
@@ -2334,13 +2352,13 @@
       <c r="AH2" s="9"/>
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK2" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AL2" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AM2" s="9" t="s">
         <v>128</v>
@@ -2352,91 +2370,91 @@
         <v>128</v>
       </c>
       <c r="AP2" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AQ2" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AR2" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AS2" s="9"/>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AW2" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AX2" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
-      <c r="BA2" s="9" t="s">
-        <v>140</v>
+      <c r="BA2" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="BB2" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC2" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BD2" s="9"/>
       <c r="BE2" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF2" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG2" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="BH2" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI2" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ2" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK2" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL2" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="BN2" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="BO2" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP2" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="BQ2" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="BG2" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="BH2" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="BI2" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BJ2" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="BK2" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="BL2" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BM2" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN2" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="BO2" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="BP2" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ2" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="BR2" s="9">
         <v>411203205</v>
       </c>
       <c r="BS2" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BT2" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BU2" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BV2" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BW2" s="9">
         <v>13501975</v>
@@ -2444,10 +2462,10 @@
       <c r="BX2" s="9"/>
       <c r="BY2" s="9"/>
       <c r="BZ2" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CA2" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CB2" s="9" t="s">
         <v>128</v>
@@ -2464,37 +2482,37 @@
       <c r="CF2" s="9"/>
       <c r="CG2" s="9"/>
       <c r="CH2" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CI2" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CJ2" s="9"/>
       <c r="CK2" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>162</v>
-      </c>
-      <c r="CM2" t="s">
         <v>163</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CL2" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="CM2" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="CN2" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="CO2" t="s">
-        <v>164</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>165</v>
-      </c>
-      <c r="CQ2" t="s">
+      <c r="CO2" s="6" t="s">
         <v>166</v>
+      </c>
+      <c r="CP2" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="CQ2" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="84" spans="1:119">
       <c r="A3" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>117</v>
@@ -2515,15 +2533,15 @@
         <v>121</v>
       </c>
       <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>168</v>
+      <c r="I3" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="J3" s="8"/>
-      <c r="K3" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>169</v>
+      <c r="K3" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>125</v>
@@ -2548,7 +2566,7 @@
         <v>130</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="X3" s="9">
         <v>800</v>
@@ -2569,223 +2587,225 @@
       <c r="AH3" s="8"/>
       <c r="AI3" s="8"/>
       <c r="AJ3" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK3" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP3" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AR3" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="AK3" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL3" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ3" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="AR3" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8"/>
       <c r="AU3" s="8"/>
       <c r="AV3" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="AW3" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AW3" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AX3" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY3" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="AX3" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY3" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ3" s="8" t="s">
-        <v>176</v>
-      </c>
       <c r="BA3" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BB3" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC3" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BD3" s="8"/>
       <c r="BE3" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF3" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="BH3" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ3" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK3" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="BN3" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="BO3" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP3" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="BQ3" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="BG3" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="BH3" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="BI3" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BJ3" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="BK3" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="BL3" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BM3" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN3" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="BO3" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="BP3" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ3" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="BR3" s="9">
         <v>411203205</v>
       </c>
       <c r="BS3" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BT3" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BU3" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BV3" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BW3" s="9">
         <v>13501975</v>
       </c>
-      <c r="BX3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="BY3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="BZ3" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="CA3" s="8"/>
+      <c r="BX3" s="8"/>
+      <c r="BY3" s="8"/>
+      <c r="BZ3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="CA3" s="12" t="s">
+        <v>160</v>
+      </c>
       <c r="CB3" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="CC3" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="CD3" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="CE3" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="CF3" s="8"/>
       <c r="CG3" s="8"/>
       <c r="CH3" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CI3" s="8"/>
       <c r="CJ3" s="8"/>
       <c r="CK3" s="8"/>
       <c r="CL3" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="CM3" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="CN3" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="CO3" s="8"/>
       <c r="CP3" s="8"/>
       <c r="CQ3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="CR3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="CS3" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="CT3" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="CR3" s="8" t="s">
+      <c r="CU3" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="CS3" s="8" t="s">
+      <c r="CV3" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="CT3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="CU3" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="CV3" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="CW3" s="16"/>
       <c r="CX3" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="CY3" s="16"/>
       <c r="CZ3" s="16" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="DA3" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="DB3" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="DC3" s="16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="DD3" s="16" t="s">
         <v>120</v>
       </c>
       <c r="DE3" s="16" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="DF3" s="16" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="DG3" s="16"/>
       <c r="DH3" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="DI3" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="DJ3" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="DK3" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="DL3" s="16" t="s">
         <v>194</v>
-      </c>
-      <c r="DI3" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="DJ3" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="DK3" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="DL3" s="16" t="s">
-        <v>197</v>
       </c>
       <c r="DM3" s="16"/>
       <c r="DN3" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="DO3" s="8" t="s">
-        <v>199</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="DO3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="72" spans="1:89">
       <c r="A4" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>117</v>
@@ -2807,7 +2827,7 @@
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9" t="s">
@@ -2816,37 +2836,39 @@
       <c r="L4" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="M4" s="9" t="s">
-        <v>201</v>
+      <c r="M4" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>126</v>
       </c>
       <c r="O4" s="9"/>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="R4" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="T4" s="9">
         <v>10000</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="V4" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="W4" s="8" t="s">
-        <v>170</v>
+      <c r="W4" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="X4" s="9">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="Y4" s="8">
         <v>5</v>
@@ -2858,7 +2880,7 @@
         <v>128</v>
       </c>
       <c r="AB4" s="9">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="AC4" s="9">
         <v>200</v>
@@ -2882,111 +2904,109 @@
         <v>200</v>
       </c>
       <c r="AJ4" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK4" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="AN4" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="AL4" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>206</v>
-      </c>
       <c r="AO4" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AR4" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AS4" s="9"/>
       <c r="AT4" s="9"/>
       <c r="AU4" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AV4" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AW4" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AX4" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AY4" s="9"/>
       <c r="AZ4" s="9"/>
-      <c r="BA4" s="9" t="s">
-        <v>140</v>
-      </c>
+      <c r="BA4" s="9"/>
       <c r="BB4" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC4" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BD4" s="9"/>
       <c r="BE4" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF4" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL4" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM4" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="BN4" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="BO4" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="BQ4" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="BG4" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="BH4" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="BI4" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BJ4" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="BK4" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="BL4" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BM4" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN4" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="BO4" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="BP4" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ4" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="BR4" s="9">
         <v>411203205</v>
       </c>
       <c r="BS4" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BT4" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BU4" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BV4" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BW4" s="9">
         <v>13501975</v>
@@ -2994,10 +3014,10 @@
       <c r="BX4" s="9"/>
       <c r="BY4" s="9"/>
       <c r="BZ4" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CA4" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CB4" s="9" t="s">
         <v>128</v>
@@ -3014,19 +3034,19 @@
       <c r="CF4" s="9"/>
       <c r="CG4" s="9"/>
       <c r="CH4" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CI4" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CJ4" s="9"/>
       <c r="CK4" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="1" ht="129" customHeight="1" spans="1:119">
       <c r="A5" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>117</v>
@@ -3044,11 +3064,11 @@
         <v>120</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9" t="s">
@@ -3057,7 +3077,7 @@
       <c r="L5" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="N5" s="9" t="s">
@@ -3084,7 +3104,7 @@
         <v>130</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="X5" s="9">
         <v>800</v>
@@ -3107,43 +3127,43 @@
       <c r="AH5" s="12"/>
       <c r="AI5" s="12"/>
       <c r="AJ5" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="AL5" s="9" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="AM5" s="9" t="s">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="AN5" s="9" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="AO5" s="9" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="AP5" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AQ5" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AR5" s="9" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="AS5" s="9"/>
       <c r="AT5" s="9"/>
       <c r="AU5" s="9"/>
       <c r="AV5" s="9" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="AW5" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AY5" s="9"/>
       <c r="AZ5" s="9"/>
@@ -3152,62 +3172,62 @@
         <v>39008846636</v>
       </c>
       <c r="BC5" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BD5" s="9"/>
       <c r="BE5" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF5" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG5" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="BH5" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BJ5" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK5" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM5" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="BN5" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="BO5" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP5" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="BQ5" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="BG5" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="BH5" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="BI5" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BJ5" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="BK5" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="BL5" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BM5" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN5" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="BO5" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="BP5" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ5" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="BR5" s="9">
         <v>411203205</v>
       </c>
       <c r="BS5" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BT5" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BU5" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BV5" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BW5" s="9">
         <v>13501975</v>
@@ -3215,10 +3235,10 @@
       <c r="BX5" s="9"/>
       <c r="BY5" s="9"/>
       <c r="BZ5" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CA5" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CB5" s="12" t="s">
         <v>128</v>
@@ -3235,93 +3255,93 @@
       <c r="CF5" s="12"/>
       <c r="CG5" s="12"/>
       <c r="CH5" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CI5" s="12"/>
       <c r="CJ5" s="12"/>
       <c r="CK5" s="8"/>
       <c r="CL5" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="CM5" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="CN5" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="CO5" s="8"/>
       <c r="CP5" s="8"/>
       <c r="CQ5" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="CR5" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="CS5" s="8"/>
       <c r="CT5" s="16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="CU5" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="CV5" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="CW5" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="CX5" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="CY5" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CZ5" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="DA5" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="DB5" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="CV5" s="16" t="s">
+      <c r="DC5" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="CW5" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="CX5" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="CY5" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="CZ5" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="DA5" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="DB5" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="DC5" s="16" t="s">
-        <v>219</v>
       </c>
       <c r="DD5" s="16" t="s">
         <v>120</v>
       </c>
       <c r="DE5" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="DF5" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="DG5" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="DH5" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="DI5" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="DF5" s="16" t="s">
+      <c r="DJ5" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="DG5" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="DH5" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="DI5" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="DJ5" s="16" t="s">
-        <v>196</v>
       </c>
       <c r="DK5" s="16"/>
       <c r="DL5" s="16" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="DM5" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="DN5" s="16"/>
       <c r="DO5" s="8" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:119">
+    <row r="6" s="3" customFormat="1" ht="12" spans="1:119">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3387,14 +3407,14 @@
       <c r="BK6" s="8"/>
       <c r="BL6" s="8"/>
       <c r="BM6" s="8"/>
-      <c r="BN6" s="14"/>
+      <c r="BN6" s="8"/>
       <c r="BO6" s="8"/>
       <c r="BP6" s="8"/>
       <c r="BQ6" s="8"/>
-      <c r="BR6" s="15"/>
+      <c r="BR6" s="8"/>
       <c r="BS6" s="8"/>
       <c r="BT6" s="8"/>
-      <c r="BU6" s="12"/>
+      <c r="BU6" s="8"/>
       <c r="BV6" s="8"/>
       <c r="BW6" s="8"/>
       <c r="BX6" s="8"/>
@@ -3419,27 +3439,27 @@
       <c r="CQ6" s="8"/>
       <c r="CR6" s="8"/>
       <c r="CS6" s="8"/>
-      <c r="CT6" s="16"/>
-      <c r="CU6" s="16"/>
-      <c r="CV6" s="16"/>
-      <c r="CW6" s="16"/>
-      <c r="CX6" s="16"/>
-      <c r="CY6" s="16"/>
-      <c r="CZ6" s="16"/>
-      <c r="DA6" s="16"/>
-      <c r="DB6" s="16"/>
-      <c r="DC6" s="16"/>
-      <c r="DD6" s="16"/>
-      <c r="DE6" s="16"/>
-      <c r="DF6" s="16"/>
-      <c r="DG6" s="16"/>
-      <c r="DH6" s="16"/>
-      <c r="DI6" s="16"/>
-      <c r="DJ6" s="16"/>
-      <c r="DK6" s="16"/>
-      <c r="DL6" s="16"/>
-      <c r="DM6" s="16"/>
-      <c r="DN6" s="16"/>
+      <c r="CT6" s="8"/>
+      <c r="CU6" s="8"/>
+      <c r="CV6" s="8"/>
+      <c r="CW6" s="8"/>
+      <c r="CX6" s="8"/>
+      <c r="CY6" s="8"/>
+      <c r="CZ6" s="8"/>
+      <c r="DA6" s="8"/>
+      <c r="DB6" s="8"/>
+      <c r="DC6" s="8"/>
+      <c r="DD6" s="8"/>
+      <c r="DE6" s="8"/>
+      <c r="DF6" s="8"/>
+      <c r="DG6" s="8"/>
+      <c r="DH6" s="8"/>
+      <c r="DI6" s="8"/>
+      <c r="DJ6" s="8"/>
+      <c r="DK6" s="8"/>
+      <c r="DL6" s="8"/>
+      <c r="DM6" s="8"/>
+      <c r="DN6" s="8"/>
       <c r="DO6" s="8"/>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:119">
